--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/70.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/70.xlsx
@@ -426,13 +426,13 @@
         <v>-5.018908837381386</v>
       </c>
       <c r="E2">
-        <v>-12.40066208746192</v>
+        <v>-17.83861670093676</v>
       </c>
       <c r="F2">
-        <v>-4.737115263643356</v>
+        <v>-4.215478960333657</v>
       </c>
       <c r="G2">
-        <v>-7.216030368073133</v>
+        <v>-7.385013854579691</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.868812261478104</v>
       </c>
       <c r="E3">
-        <v>-13.29181595895736</v>
+        <v>-18.86813809573657</v>
       </c>
       <c r="F3">
-        <v>-4.923085890028622</v>
+        <v>-4.073783208373374</v>
       </c>
       <c r="G3">
-        <v>-6.04288227695822</v>
+        <v>-8.156880789242926</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.786283409506838</v>
       </c>
       <c r="E4">
-        <v>-12.81318795566466</v>
+        <v>-18.67977169091351</v>
       </c>
       <c r="F4">
-        <v>-4.759110563249937</v>
+        <v>-3.996034333866706</v>
       </c>
       <c r="G4">
-        <v>-5.872448771505461</v>
+        <v>-8.531713997381367</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.770180804043314</v>
       </c>
       <c r="E5">
-        <v>-14.26552844008664</v>
+        <v>-17.22254498303725</v>
       </c>
       <c r="F5">
-        <v>-4.660269893361446</v>
+        <v>-3.692852048973851</v>
       </c>
       <c r="G5">
-        <v>-6.428137082454286</v>
+        <v>-7.540010286182829</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.790938900639939</v>
       </c>
       <c r="E6">
-        <v>-15.13864087113552</v>
+        <v>-18.7194365947467</v>
       </c>
       <c r="F6">
-        <v>-3.861092295782814</v>
+        <v>-3.740423407261821</v>
       </c>
       <c r="G6">
-        <v>-6.74418162290635</v>
+        <v>-7.34395646880165</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.828412951700559</v>
       </c>
       <c r="E7">
-        <v>-15.5506006800873</v>
+        <v>-18.43538353414156</v>
       </c>
       <c r="F7">
-        <v>-4.246704889868377</v>
+        <v>-3.916289198053625</v>
       </c>
       <c r="G7">
-        <v>-6.889051095704857</v>
+        <v>-9.230421186172247</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.862178813775233</v>
       </c>
       <c r="E8">
-        <v>-15.99041060418626</v>
+        <v>-19.66878588571471</v>
       </c>
       <c r="F8">
-        <v>-4.079348350960228</v>
+        <v>-3.66886682288452</v>
       </c>
       <c r="G8">
-        <v>-7.852188109445024</v>
+        <v>-9.457683516352136</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.874160327703954</v>
       </c>
       <c r="E9">
-        <v>-16.09938833118084</v>
+        <v>-19.44705821287715</v>
       </c>
       <c r="F9">
-        <v>-4.005405913621319</v>
+        <v>-3.045909766222752</v>
       </c>
       <c r="G9">
-        <v>-7.339798423604326</v>
+        <v>-9.021009317540109</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.851573288995516</v>
       </c>
       <c r="E10">
-        <v>-17.64231640965226</v>
+        <v>-22.53370232429732</v>
       </c>
       <c r="F10">
-        <v>-3.925657610396407</v>
+        <v>-3.210789389079153</v>
       </c>
       <c r="G10">
-        <v>-7.599894744442706</v>
+        <v>-9.291417987733318</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.790264685062363</v>
       </c>
       <c r="E11">
-        <v>-16.49195268595777</v>
+        <v>-20.90401774078695</v>
       </c>
       <c r="F11">
-        <v>-3.529832488715134</v>
+        <v>-3.67490945280488</v>
       </c>
       <c r="G11">
-        <v>-7.040938925046619</v>
+        <v>-7.863784950469091</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.69121769023972</v>
       </c>
       <c r="E12">
-        <v>-16.57243272602209</v>
+        <v>-22.63855913994493</v>
       </c>
       <c r="F12">
-        <v>-3.698163798614235</v>
+        <v>-3.610423323487058</v>
       </c>
       <c r="G12">
-        <v>-7.36071776086698</v>
+        <v>-8.761429441805856</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.557949815581601</v>
       </c>
       <c r="E13">
-        <v>-17.46184766349858</v>
+        <v>-21.2954092207959</v>
       </c>
       <c r="F13">
-        <v>-3.451010653450755</v>
+        <v>-3.396264315512886</v>
       </c>
       <c r="G13">
-        <v>-6.540424166055287</v>
+        <v>-9.379018333247974</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.401340878084898</v>
       </c>
       <c r="E14">
-        <v>-17.53630030465869</v>
+        <v>-21.96348140572548</v>
       </c>
       <c r="F14">
-        <v>-3.464004960486935</v>
+        <v>-3.798001411376495</v>
       </c>
       <c r="G14">
-        <v>-6.920127186681996</v>
+        <v>-7.331151278655749</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.233390392546317</v>
       </c>
       <c r="E15">
-        <v>-18.33797605823658</v>
+        <v>-23.2456961786273</v>
       </c>
       <c r="F15">
-        <v>-3.19415651770225</v>
+        <v>-3.482577079757294</v>
       </c>
       <c r="G15">
-        <v>-5.729562315484977</v>
+        <v>-7.474249609590746</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.063222715216084</v>
       </c>
       <c r="E16">
-        <v>-19.5374193832262</v>
+        <v>-23.05913663493331</v>
       </c>
       <c r="F16">
-        <v>-3.225435501385137</v>
+        <v>-3.189537639399871</v>
       </c>
       <c r="G16">
-        <v>-5.524967290612478</v>
+        <v>-7.169318570514017</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.899930890499309</v>
       </c>
       <c r="E17">
-        <v>-19.60204976426367</v>
+        <v>-24.09075471319867</v>
       </c>
       <c r="F17">
-        <v>-2.645822891923031</v>
+        <v>-2.541133596088822</v>
       </c>
       <c r="G17">
-        <v>-6.267429959795907</v>
+        <v>-4.988718503070253</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.75145062450471</v>
       </c>
       <c r="E18">
-        <v>-21.55869922807586</v>
+        <v>-24.68153490376534</v>
       </c>
       <c r="F18">
-        <v>-2.676766921804802</v>
+        <v>-2.854839606789771</v>
       </c>
       <c r="G18">
-        <v>-4.553130163195108</v>
+        <v>-5.306567290841219</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.622087495970184</v>
       </c>
       <c r="E19">
-        <v>-21.54663084484542</v>
+        <v>-26.50300488997455</v>
       </c>
       <c r="F19">
-        <v>-1.897746733117884</v>
+        <v>-2.746500660673432</v>
       </c>
       <c r="G19">
-        <v>-4.847411177272002</v>
+        <v>-4.22370770821885</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.510927814419926</v>
       </c>
       <c r="E20">
-        <v>-21.25017429393328</v>
+        <v>-26.77239928021686</v>
       </c>
       <c r="F20">
-        <v>-2.251133287383127</v>
+        <v>-2.564568484372537</v>
       </c>
       <c r="G20">
-        <v>-4.964624352635438</v>
+        <v>-5.693311841829958</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.419010933305563</v>
       </c>
       <c r="E21">
-        <v>-22.7027774298477</v>
+        <v>-30.2397680511209</v>
       </c>
       <c r="F21">
-        <v>-1.822231675804943</v>
+        <v>-2.636542375258556</v>
       </c>
       <c r="G21">
-        <v>-3.671611339180133</v>
+        <v>-5.527314467399822</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.34441116601048</v>
       </c>
       <c r="E22">
-        <v>-22.20893828236323</v>
+        <v>-26.60177543655585</v>
       </c>
       <c r="F22">
-        <v>-1.722280828069728</v>
+        <v>-1.881129698800136</v>
       </c>
       <c r="G22">
-        <v>-4.004198675691934</v>
+        <v>-4.511940355595495</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.281299601383739</v>
       </c>
       <c r="E23">
-        <v>-22.49933573505311</v>
+        <v>-29.97955287769215</v>
       </c>
       <c r="F23">
-        <v>-1.075017844870753</v>
+        <v>-2.470895446886124</v>
       </c>
       <c r="G23">
-        <v>-3.688816244347725</v>
+        <v>-5.186344829582586</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.225081306264468</v>
       </c>
       <c r="E24">
-        <v>-24.16330539527555</v>
+        <v>-28.95666343307657</v>
       </c>
       <c r="F24">
-        <v>-1.037884692271444</v>
+        <v>-2.091053877156423</v>
       </c>
       <c r="G24">
-        <v>-4.202801613138352</v>
+        <v>-4.501204256411639</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.171521494641172</v>
       </c>
       <c r="E25">
-        <v>-25.26136071570745</v>
+        <v>-27.73405243506371</v>
       </c>
       <c r="F25">
-        <v>-1.333393922003995</v>
+        <v>-1.461135641143341</v>
       </c>
       <c r="G25">
-        <v>-4.579905855516733</v>
+        <v>-5.188043139444233</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.114783764941718</v>
       </c>
       <c r="E26">
-        <v>-24.77612114036355</v>
+        <v>-30.96792629342126</v>
       </c>
       <c r="F26">
-        <v>-1.175102515755822</v>
+        <v>-2.135787234443926</v>
       </c>
       <c r="G26">
-        <v>-4.225276906804464</v>
+        <v>-5.881622293194781</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.047870949839675</v>
       </c>
       <c r="E27">
-        <v>-25.51194835339589</v>
+        <v>-30.28826121503204</v>
       </c>
       <c r="F27">
-        <v>-1.562317028374852</v>
+        <v>-1.072342965579576</v>
       </c>
       <c r="G27">
-        <v>-3.669363478758968</v>
+        <v>-5.04610349944798</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.967946529906085</v>
       </c>
       <c r="E28">
-        <v>-24.11987280106799</v>
+        <v>-28.84620942355549</v>
       </c>
       <c r="F28">
-        <v>-0.5863257920140257</v>
+        <v>-2.318444748054092</v>
       </c>
       <c r="G28">
-        <v>-4.917425904882048</v>
+        <v>-6.057554614788271</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.870282977447516</v>
       </c>
       <c r="E29">
-        <v>-24.90204441709484</v>
+        <v>-30.75929043893987</v>
       </c>
       <c r="F29">
-        <v>-1.359036496333833</v>
+        <v>-1.170465424835415</v>
       </c>
       <c r="G29">
-        <v>-4.241971987959008</v>
+        <v>-5.230196315795772</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.748905976092042</v>
       </c>
       <c r="E30">
-        <v>-25.67281333557037</v>
+        <v>-27.60189344962386</v>
       </c>
       <c r="F30">
-        <v>-0.5329422330163928</v>
+        <v>-1.404762045377358</v>
       </c>
       <c r="G30">
-        <v>-4.260938103353493</v>
+        <v>-5.522954478924602</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.601060608643736</v>
       </c>
       <c r="E31">
-        <v>-25.16475025122781</v>
+        <v>-29.74181478500047</v>
       </c>
       <c r="F31">
-        <v>-0.8097803618588699</v>
+        <v>-1.558719640387931</v>
       </c>
       <c r="G31">
-        <v>-4.208916190749385</v>
+        <v>-6.115032306441097</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.424996873112907</v>
       </c>
       <c r="E32">
-        <v>-24.41067328794455</v>
+        <v>-29.42369854290964</v>
       </c>
       <c r="F32">
-        <v>-0.8691051935982739</v>
+        <v>-1.646457739956234</v>
       </c>
       <c r="G32">
-        <v>-4.430815437155655</v>
+        <v>-3.23156038391805</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.219012048464904</v>
       </c>
       <c r="E33">
-        <v>-25.65510700220038</v>
+        <v>-29.44813645289204</v>
       </c>
       <c r="F33">
-        <v>-1.182241070169666</v>
+        <v>-2.116456520040072</v>
       </c>
       <c r="G33">
-        <v>-3.795015234702006</v>
+        <v>-5.385609876136858</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.98339087849966</v>
       </c>
       <c r="E34">
-        <v>-25.57258914883261</v>
+        <v>-28.51439454759146</v>
       </c>
       <c r="F34">
-        <v>-0.7620696374503411</v>
+        <v>-1.250991327664807</v>
       </c>
       <c r="G34">
-        <v>-4.449039990349343</v>
+        <v>-4.936517821007025</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.723904685518282</v>
       </c>
       <c r="E35">
-        <v>-24.08879388395335</v>
+        <v>-28.97555169816257</v>
       </c>
       <c r="F35">
-        <v>-0.7800716225911413</v>
+        <v>-1.531333405845194</v>
       </c>
       <c r="G35">
-        <v>-5.123172999602213</v>
+        <v>-4.578833238762009</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.444345042600104</v>
       </c>
       <c r="E36">
-        <v>-25.01166971587252</v>
+        <v>-28.8360656417783</v>
       </c>
       <c r="F36">
-        <v>-1.07264703711534</v>
+        <v>-1.652967563121648</v>
       </c>
       <c r="G36">
-        <v>-3.988741738569077</v>
+        <v>-4.50960311044477</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.149246005337198</v>
       </c>
       <c r="E37">
-        <v>-22.42325284325024</v>
+        <v>-29.66672362900528</v>
       </c>
       <c r="F37">
-        <v>-1.171187594732856</v>
+        <v>-1.46202489201486</v>
       </c>
       <c r="G37">
-        <v>-4.443935129127786</v>
+        <v>-6.210753420163583</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8476175820913399</v>
       </c>
       <c r="E38">
-        <v>-24.73149755749196</v>
+        <v>-28.23970637123419</v>
       </c>
       <c r="F38">
-        <v>-0.9922216996115788</v>
+        <v>-1.389775436299555</v>
       </c>
       <c r="G38">
-        <v>-3.900611705768139</v>
+        <v>-4.068472917336885</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.5477076868147015</v>
       </c>
       <c r="E39">
-        <v>-24.41231259553533</v>
+        <v>-27.40689735885357</v>
       </c>
       <c r="F39">
-        <v>-0.8093266301140966</v>
+        <v>-1.66099536840701</v>
       </c>
       <c r="G39">
-        <v>-3.558811121020546</v>
+        <v>-4.820844049319351</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.2562224252462504</v>
       </c>
       <c r="E40">
-        <v>-24.29962604832846</v>
+        <v>-27.62168288103738</v>
       </c>
       <c r="F40">
-        <v>-0.5975526832485759</v>
+        <v>-1.489784089300683</v>
       </c>
       <c r="G40">
-        <v>-4.321872004549319</v>
+        <v>-3.693494045194715</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.02058902339571491</v>
       </c>
       <c r="E41">
-        <v>-24.78275535478478</v>
+        <v>-27.36755850514894</v>
       </c>
       <c r="F41">
-        <v>-1.159180728334952</v>
+        <v>-1.144221834110668</v>
       </c>
       <c r="G41">
-        <v>-4.016500662915866</v>
+        <v>-4.272813030202859</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.2744857779428425</v>
       </c>
       <c r="E42">
-        <v>-23.50172251359896</v>
+        <v>-29.00361918006211</v>
       </c>
       <c r="F42">
-        <v>-0.6251527180898968</v>
+        <v>-1.337805334831452</v>
       </c>
       <c r="G42">
-        <v>-4.79649829742355</v>
+        <v>-4.195521723497495</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.5022354824949865</v>
       </c>
       <c r="E43">
-        <v>-21.68877964394619</v>
+        <v>-27.27154127076431</v>
       </c>
       <c r="F43">
-        <v>-0.6959277435979281</v>
+        <v>-1.3576380840105</v>
       </c>
       <c r="G43">
-        <v>-3.630749275588909</v>
+        <v>-2.692133472658124</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.7022832886804919</v>
       </c>
       <c r="E44">
-        <v>-22.4295474221209</v>
+        <v>-28.06428687359906</v>
       </c>
       <c r="F44">
-        <v>-0.9090327952853755</v>
+        <v>-0.5878057651920038</v>
       </c>
       <c r="G44">
-        <v>-3.744433409407481</v>
+        <v>-1.836284618754658</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.8712848603527407</v>
       </c>
       <c r="E45">
-        <v>-23.20048389413472</v>
+        <v>-26.907682912722</v>
       </c>
       <c r="F45">
-        <v>-0.426474435439145</v>
+        <v>-0.7946290473658607</v>
       </c>
       <c r="G45">
-        <v>-2.668135328043947</v>
+        <v>-3.505117382919106</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.008930604193128</v>
       </c>
       <c r="E46">
-        <v>-22.66614207512565</v>
+        <v>-28.01080559556847</v>
       </c>
       <c r="F46">
-        <v>-0.7301943884902914</v>
+        <v>-0.547751467031667</v>
       </c>
       <c r="G46">
-        <v>-4.061173164422791</v>
+        <v>-3.488170700303577</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.116629538976753</v>
       </c>
       <c r="E47">
-        <v>-21.00786923520486</v>
+        <v>-27.37593165358912</v>
       </c>
       <c r="F47">
-        <v>-0.7099490839202712</v>
+        <v>-0.7729496970894101</v>
       </c>
       <c r="G47">
-        <v>-3.525619591443813</v>
+        <v>-2.536011455571634</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.195819444309745</v>
       </c>
       <c r="E48">
-        <v>-21.79177525677664</v>
+        <v>-24.38265109078509</v>
       </c>
       <c r="F48">
-        <v>-0.5183483830056183</v>
+        <v>-0.8479049143612437</v>
       </c>
       <c r="G48">
-        <v>-3.924169547825592</v>
+        <v>-4.951511281754384</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.247143803019414</v>
       </c>
       <c r="E49">
-        <v>-22.5983961039709</v>
+        <v>-24.11052150224215</v>
       </c>
       <c r="F49">
-        <v>-0.5832803255386356</v>
+        <v>-1.491821526960895</v>
       </c>
       <c r="G49">
-        <v>-3.859345755621123</v>
+        <v>-5.119888938427256</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.273609214413046</v>
       </c>
       <c r="E50">
-        <v>-20.58723739852839</v>
+        <v>-24.38979702276919</v>
       </c>
       <c r="F50">
-        <v>-0.8930975463642238</v>
+        <v>-0.918029828590987</v>
       </c>
       <c r="G50">
-        <v>-3.274090962461067</v>
+        <v>-6.276795493126505</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.278165600987409</v>
       </c>
       <c r="E51">
-        <v>-19.61513252567183</v>
+        <v>-25.34267852346319</v>
       </c>
       <c r="F51">
-        <v>-0.3297139632705834</v>
+        <v>-0.7553887740460598</v>
       </c>
       <c r="G51">
-        <v>-3.602268652314559</v>
+        <v>-4.365408988936275</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.262849528137915</v>
       </c>
       <c r="E52">
-        <v>-19.60896927254739</v>
+        <v>-26.75858743449346</v>
       </c>
       <c r="F52">
-        <v>-0.552876339374029</v>
+        <v>-1.100155217013566</v>
       </c>
       <c r="G52">
-        <v>-3.141569824524041</v>
+        <v>-4.313115611597946</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.230771827371705</v>
       </c>
       <c r="E53">
-        <v>-18.99766603777796</v>
+        <v>-24.57072314479764</v>
       </c>
       <c r="F53">
-        <v>-0.64337246279407</v>
+        <v>-0.9602625142380108</v>
       </c>
       <c r="G53">
-        <v>-3.228491508203145</v>
+        <v>-4.482413599930736</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.184920672027106</v>
       </c>
       <c r="E54">
-        <v>-19.56174634559541</v>
+        <v>-24.66944840663886</v>
       </c>
       <c r="F54">
-        <v>-1.055045729571146</v>
+        <v>-0.2831981449752536</v>
       </c>
       <c r="G54">
-        <v>-3.271492184212739</v>
+        <v>-3.784749232984726</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.128414815550047</v>
       </c>
       <c r="E55">
-        <v>-18.01578871801285</v>
+        <v>-23.61129799916256</v>
       </c>
       <c r="F55">
-        <v>-0.426847398182231</v>
+        <v>-1.60541283374579</v>
       </c>
       <c r="G55">
-        <v>-3.722093848108479</v>
+        <v>-4.984358514595034</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.064974243950798</v>
       </c>
       <c r="E56">
-        <v>-19.03596334246083</v>
+        <v>-23.90592957504961</v>
       </c>
       <c r="F56">
-        <v>-0.4874764117429994</v>
+        <v>-0.819662686771212</v>
       </c>
       <c r="G56">
-        <v>-5.117773499827662</v>
+        <v>-4.579028560948826</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9987796002839672</v>
       </c>
       <c r="E57">
-        <v>-18.3685704286324</v>
+        <v>-21.26879537905281</v>
       </c>
       <c r="F57">
-        <v>-1.288173575147495</v>
+        <v>-1.147989470483499</v>
       </c>
       <c r="G57">
-        <v>-4.803033314318071</v>
+        <v>-4.582766166862664</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.9330311833806973</v>
       </c>
       <c r="E58">
-        <v>-16.69844204375952</v>
+        <v>-23.01789129367145</v>
       </c>
       <c r="F58">
-        <v>-0.6352227121532186</v>
+        <v>-1.243057752881414</v>
       </c>
       <c r="G58">
-        <v>-4.949846077348131</v>
+        <v>-5.125705566939756</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.8713401815074491</v>
       </c>
       <c r="E59">
-        <v>-16.74533439210895</v>
+        <v>-21.84941367394627</v>
       </c>
       <c r="F59">
-        <v>-0.1486821237826156</v>
+        <v>-0.7693396394551659</v>
       </c>
       <c r="G59">
-        <v>-4.17914445471472</v>
+        <v>-6.491206285522942</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.8166962464655632</v>
       </c>
       <c r="E60">
-        <v>-17.93514565288426</v>
+        <v>-22.31315205470175</v>
       </c>
       <c r="F60">
-        <v>-1.250178094677229</v>
+        <v>-1.128102083450368</v>
       </c>
       <c r="G60">
-        <v>-5.824002248083766</v>
+        <v>-5.306547427567984</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.7705380568802429</v>
       </c>
       <c r="E61">
-        <v>-17.30412091381143</v>
+        <v>-21.06619145194965</v>
       </c>
       <c r="F61">
-        <v>-1.13283815599049</v>
+        <v>-1.255965747945203</v>
       </c>
       <c r="G61">
-        <v>-4.813772724047467</v>
+        <v>-4.223042288565456</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.7333839034853112</v>
       </c>
       <c r="E62">
-        <v>-18.30813341452603</v>
+        <v>-21.67445608065993</v>
       </c>
       <c r="F62">
-        <v>-1.293691206556886</v>
+        <v>-0.9428853010808514</v>
       </c>
       <c r="G62">
-        <v>-4.987301589579445</v>
+        <v>-6.384189590420462</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.7058109377967396</v>
       </c>
       <c r="E63">
-        <v>-16.56058623801802</v>
+        <v>-22.20537890179321</v>
       </c>
       <c r="F63">
-        <v>-1.143113239969861</v>
+        <v>-0.8388904602905624</v>
       </c>
       <c r="G63">
-        <v>-5.061533952206523</v>
+        <v>-6.714346986506438</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.6880675853625903</v>
       </c>
       <c r="E64">
-        <v>-16.86281659328994</v>
+        <v>-21.58649953000895</v>
       </c>
       <c r="F64">
-        <v>-1.539115736713664</v>
+        <v>-1.216065069258663</v>
       </c>
       <c r="G64">
-        <v>-4.750004995870026</v>
+        <v>-6.149971804062565</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.6794952669293175</v>
       </c>
       <c r="E65">
-        <v>-16.32088052337001</v>
+        <v>-21.90228813645983</v>
       </c>
       <c r="F65">
-        <v>-1.20418648303991</v>
+        <v>-2.237570429923304</v>
       </c>
       <c r="G65">
-        <v>-5.818275004300827</v>
+        <v>-5.715317038029493</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.6798126891399393</v>
       </c>
       <c r="E66">
-        <v>-16.07236239830307</v>
+        <v>-21.48530624983355</v>
       </c>
       <c r="F66">
-        <v>-1.51202723888303</v>
+        <v>-1.119835138571774</v>
       </c>
       <c r="G66">
-        <v>-5.62575353901005</v>
+        <v>-5.560426543883612</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.6887523849740953</v>
       </c>
       <c r="E67">
-        <v>-16.57712875356804</v>
+        <v>-19.37934394104045</v>
       </c>
       <c r="F67">
-        <v>-1.132420849481771</v>
+        <v>-1.874686391283171</v>
       </c>
       <c r="G67">
-        <v>-4.683506067622686</v>
+        <v>-7.133018438675908</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.7057882465073266</v>
       </c>
       <c r="E68">
-        <v>-16.01874073757824</v>
+        <v>-19.39527058412543</v>
       </c>
       <c r="F68">
-        <v>-1.654708055922716</v>
+        <v>-2.023815266957568</v>
       </c>
       <c r="G68">
-        <v>-5.796213528827124</v>
+        <v>-5.532051858066519</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.7299102584417613</v>
       </c>
       <c r="E69">
-        <v>-16.21420778964533</v>
+        <v>-19.72093579238704</v>
       </c>
       <c r="F69">
-        <v>-1.178335651382192</v>
+        <v>-1.923336253299555</v>
       </c>
       <c r="G69">
-        <v>-6.048503583283903</v>
+        <v>-6.475762590582242</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.7597414094460714</v>
       </c>
       <c r="E70">
-        <v>-15.42469098877804</v>
+        <v>-19.56343546640027</v>
       </c>
       <c r="F70">
-        <v>-1.508928718259472</v>
+        <v>-1.508720460931592</v>
       </c>
       <c r="G70">
-        <v>-5.209002203253358</v>
+        <v>-6.104127369434737</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.7932154400325283</v>
       </c>
       <c r="E71">
-        <v>-15.58975386635762</v>
+        <v>-21.41426807807522</v>
       </c>
       <c r="F71">
-        <v>-1.621823986294531</v>
+        <v>-1.488867915428601</v>
       </c>
       <c r="G71">
-        <v>-6.013044330012769</v>
+        <v>-7.927092512816573</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.827041579079809</v>
       </c>
       <c r="E72">
-        <v>-16.01920264192702</v>
+        <v>-18.8092951044809</v>
       </c>
       <c r="F72">
-        <v>-1.76632685698993</v>
+        <v>-2.103984835955986</v>
       </c>
       <c r="G72">
-        <v>-6.230762357402939</v>
+        <v>-7.181200118454461</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.8580182616640372</v>
       </c>
       <c r="E73">
-        <v>-14.62810071151077</v>
+        <v>-19.2958886935531</v>
       </c>
       <c r="F73">
-        <v>-1.539012003976203</v>
+        <v>-1.442018727038071</v>
       </c>
       <c r="G73">
-        <v>-6.247560065469201</v>
+        <v>-6.835178588144297</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.8831304814033225</v>
       </c>
       <c r="E74">
-        <v>-15.96178159150976</v>
+        <v>-19.80232152725289</v>
       </c>
       <c r="F74">
-        <v>-2.101218101721714</v>
+        <v>-1.984125221157783</v>
       </c>
       <c r="G74">
-        <v>-5.672697074756917</v>
+        <v>-7.436502769351976</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.8993637938024847</v>
       </c>
       <c r="E75">
-        <v>-15.93114193637387</v>
+        <v>-19.77559900213363</v>
       </c>
       <c r="F75">
-        <v>-1.991472032899506</v>
+        <v>-2.989765015961551</v>
       </c>
       <c r="G75">
-        <v>-5.782673397571505</v>
+        <v>-6.684340201738484</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.9042048631743073</v>
       </c>
       <c r="E76">
-        <v>-17.31583154759526</v>
+        <v>-21.87759889617001</v>
       </c>
       <c r="F76">
-        <v>-1.865104970494762</v>
+        <v>-2.145033701431219</v>
       </c>
       <c r="G76">
-        <v>-5.205052722425007</v>
+        <v>-6.928439966531106</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.8962024075992501</v>
       </c>
       <c r="E77">
-        <v>-17.53700674660389</v>
+        <v>-21.73183184633711</v>
       </c>
       <c r="F77">
-        <v>-1.762949604125256</v>
+        <v>-2.494852166268977</v>
       </c>
       <c r="G77">
-        <v>-5.207072155203963</v>
+        <v>-7.421744357337905</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.8743517152998117</v>
       </c>
       <c r="E78">
-        <v>-18.10491361495781</v>
+        <v>-20.96279280493251</v>
       </c>
       <c r="F78">
-        <v>-1.982882012014163</v>
+        <v>-2.064177595918458</v>
       </c>
       <c r="G78">
-        <v>-5.618056520631245</v>
+        <v>-7.395753264309088</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.8376021466002803</v>
       </c>
       <c r="E79">
-        <v>-17.6396808377798</v>
+        <v>-21.25324912778449</v>
       </c>
       <c r="F79">
-        <v>-2.424444560533328</v>
+        <v>-2.078828459342188</v>
       </c>
       <c r="G79">
-        <v>-5.862586656343972</v>
+        <v>-8.286207250734554</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.7864262839429788</v>
       </c>
       <c r="E80">
-        <v>-18.01325277256856</v>
+        <v>-21.43966828878424</v>
       </c>
       <c r="F80">
-        <v>-1.64841757602659</v>
+        <v>-2.226873288317468</v>
       </c>
       <c r="G80">
-        <v>-5.775976163945559</v>
+        <v>-7.360101999396676</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.7201171592795186</v>
       </c>
       <c r="E81">
-        <v>-17.59234017050361</v>
+        <v>-21.06503216260368</v>
       </c>
       <c r="F81">
-        <v>-1.950862645815808</v>
+        <v>-2.504896821037652</v>
       </c>
       <c r="G81">
-        <v>-5.961025727954201</v>
+        <v>-6.673074415268344</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.6369103367346481</v>
       </c>
       <c r="E82">
-        <v>-19.10043522690803</v>
+        <v>-24.25659195983356</v>
       </c>
       <c r="F82">
-        <v>-2.368365534067617</v>
+        <v>-2.709532213489329</v>
       </c>
       <c r="G82">
-        <v>-5.186089917576062</v>
+        <v>-7.872488374691835</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.5352869315528118</v>
       </c>
       <c r="E83">
-        <v>-21.20229473825018</v>
+        <v>-23.68755750145173</v>
       </c>
       <c r="F83">
-        <v>-1.76593805718769</v>
+        <v>-2.365704908129679</v>
       </c>
       <c r="G83">
-        <v>-5.090862075138927</v>
+        <v>-7.04134281160241</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.41394869611542</v>
       </c>
       <c r="E84">
-        <v>-21.51925169099504</v>
+        <v>-24.11725534309156</v>
       </c>
       <c r="F84">
-        <v>-1.881958768846868</v>
+        <v>-1.821133375752586</v>
       </c>
       <c r="G84">
-        <v>-5.426362691725286</v>
+        <v>-6.678142860488968</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.2683736420602624</v>
       </c>
       <c r="E85">
-        <v>-23.34056318061399</v>
+        <v>-22.57310004816405</v>
       </c>
       <c r="F85">
-        <v>-1.883268493638937</v>
+        <v>-2.283410797645698</v>
       </c>
       <c r="G85">
-        <v>-4.563098215813853</v>
+        <v>-5.935822544763729</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.09320753641996679</v>
       </c>
       <c r="E86">
-        <v>-23.57057796088559</v>
+        <v>-24.23091098373607</v>
       </c>
       <c r="F86">
-        <v>-1.577946622054323</v>
+        <v>-2.246150948573155</v>
       </c>
       <c r="G86">
-        <v>-4.529055876033527</v>
+        <v>-7.35081922970456</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.1127136642311288</v>
       </c>
       <c r="E87">
-        <v>-24.85500262910316</v>
+        <v>-26.61498046676222</v>
       </c>
       <c r="F87">
-        <v>-1.999062735352207</v>
+        <v>-2.426829621641979</v>
       </c>
       <c r="G87">
-        <v>-5.082506258197806</v>
+        <v>-6.36616366995913</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.3572203571177245</v>
       </c>
       <c r="E88">
-        <v>-27.21704108608199</v>
+        <v>-28.36300766151504</v>
       </c>
       <c r="F88">
-        <v>-1.342755999523115</v>
+        <v>-2.481770755407447</v>
       </c>
       <c r="G88">
-        <v>-5.105084178775636</v>
+        <v>-4.988046462325781</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.6484513159831327</v>
       </c>
       <c r="E89">
-        <v>-27.92979119557125</v>
+        <v>-29.80751841437776</v>
       </c>
       <c r="F89">
-        <v>-1.693591203558585</v>
+        <v>-2.05500239569736</v>
       </c>
       <c r="G89">
-        <v>-5.05968666779561</v>
+        <v>-6.875885056095176</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.9914270485699518</v>
       </c>
       <c r="E90">
-        <v>-28.82238059332713</v>
+        <v>-31.49859778424712</v>
       </c>
       <c r="F90">
-        <v>-1.668374646120001</v>
+        <v>-3.063514241178777</v>
       </c>
       <c r="G90">
-        <v>-3.58622905917679</v>
+        <v>-5.324997097858342</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.390037351639312</v>
       </c>
       <c r="E91">
-        <v>-30.3970442176443</v>
+        <v>-33.41514534648438</v>
       </c>
       <c r="F91">
-        <v>-1.180430894308318</v>
+        <v>-1.946649196227781</v>
       </c>
       <c r="G91">
-        <v>-5.334200414457515</v>
+        <v>-6.015795393355903</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.853011675670077</v>
       </c>
       <c r="E92">
-        <v>-32.41881540192379</v>
+        <v>-34.23039520090025</v>
       </c>
       <c r="F92">
-        <v>-1.216670836771319</v>
+        <v>-1.704221037663015</v>
       </c>
       <c r="G92">
-        <v>-3.178541997106622</v>
+        <v>-5.201854735434072</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.3855358069478</v>
       </c>
       <c r="E93">
-        <v>-33.26274408223024</v>
+        <v>-36.07591591256421</v>
       </c>
       <c r="F93">
-        <v>-1.57288113868379</v>
+        <v>-1.549863556908794</v>
       </c>
       <c r="G93">
-        <v>-5.00849239157632</v>
+        <v>-4.99045653947837</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.980846945159985</v>
       </c>
       <c r="E94">
-        <v>-35.70908008286186</v>
+        <v>-36.78581534766564</v>
       </c>
       <c r="F94">
-        <v>-1.707036866780666</v>
+        <v>-1.57283283565337</v>
       </c>
       <c r="G94">
-        <v>-2.856651033232206</v>
+        <v>-5.86904884123663</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.639716295675222</v>
       </c>
       <c r="E95">
-        <v>-37.49306788970959</v>
+        <v>-40.10242216190633</v>
       </c>
       <c r="F95">
-        <v>-1.526161814178327</v>
+        <v>-1.694949231381075</v>
       </c>
       <c r="G95">
-        <v>-4.854889699645216</v>
+        <v>-5.531581760599942</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.362158996965376</v>
       </c>
       <c r="E96">
-        <v>-40.11647175251512</v>
+        <v>-40.70744666746413</v>
       </c>
       <c r="F96">
-        <v>-1.299781347654708</v>
+        <v>-1.686905589036557</v>
       </c>
       <c r="G96">
-        <v>-4.281158915507362</v>
+        <v>-5.95707624712585</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.128121237152449</v>
       </c>
       <c r="E97">
-        <v>-43.03121951907814</v>
+        <v>-44.7400029580805</v>
       </c>
       <c r="F97">
-        <v>-1.302289145971806</v>
+        <v>-1.601688749285634</v>
       </c>
       <c r="G97">
-        <v>-4.743562674250604</v>
+        <v>-4.329959667301758</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.936669275909814</v>
       </c>
       <c r="E98">
-        <v>-44.39276183540933</v>
+        <v>-46.08069165160636</v>
       </c>
       <c r="F98">
-        <v>-1.238769869115361</v>
+        <v>-1.907705867767125</v>
       </c>
       <c r="G98">
-        <v>-5.48862412168236</v>
+        <v>-6.801132937818433</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.755692682668421</v>
       </c>
       <c r="E99">
-        <v>-48.1342549876567</v>
+        <v>-46.41161441819088</v>
       </c>
       <c r="F99">
-        <v>-1.372626276794219</v>
+        <v>-1.751133574290162</v>
       </c>
       <c r="G99">
-        <v>-4.614643409860306</v>
+        <v>-6.404877189495368</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.60214843525095</v>
       </c>
       <c r="E100">
-        <v>-49.68647775902886</v>
+        <v>-47.42759341147075</v>
       </c>
       <c r="F100">
-        <v>-1.472561287470279</v>
+        <v>-1.585079633497463</v>
       </c>
       <c r="G100">
-        <v>-5.040273628753323</v>
+        <v>-5.637320585124264</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.397876696141452</v>
       </c>
       <c r="E101">
-        <v>-50.44822595728112</v>
+        <v>-51.846188525819</v>
       </c>
       <c r="F101">
-        <v>-1.495391991947254</v>
+        <v>-1.249843140876114</v>
       </c>
       <c r="G101">
-        <v>-6.329168323557774</v>
+        <v>-6.505094024060185</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.219479631168706</v>
       </c>
       <c r="E102">
-        <v>-53.63751585691465</v>
+        <v>-53.71462897655427</v>
       </c>
       <c r="F102">
-        <v>-1.399759118390485</v>
+        <v>-1.130203661200156</v>
       </c>
       <c r="G102">
-        <v>-5.195644152002399</v>
+        <v>-6.907818578366985</v>
       </c>
     </row>
   </sheetData>
